--- a/data_cuaca_aceh_besar.xlsx
+++ b/data_cuaca_aceh_besar.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2327"/>
+  <dimension ref="A1:E2382"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39938,67 +39938,1002 @@
         <v>46153</v>
       </c>
       <c r="B2324" t="n">
-        <v>5</v>
+        <v>0.2</v>
       </c>
       <c r="C2324" t="n">
         <v>3</v>
       </c>
       <c r="D2324" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="E2324" t="n">
-        <v>28.5</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="2325">
       <c r="A2325" s="2" t="n">
-        <v>46154.94222322917</v>
+        <v>46154</v>
       </c>
       <c r="B2325" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="C2325" t="n">
-        <v>2.27</v>
+        <v>3</v>
       </c>
       <c r="D2325" t="n">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E2325" t="n">
-        <v>25.7</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="2326">
       <c r="A2326" s="2" t="n">
-        <v>46156.65930792824</v>
+        <v>46155</v>
       </c>
       <c r="B2326" t="n">
         <v>0</v>
       </c>
       <c r="C2326" t="n">
-        <v>2.48</v>
+        <v>5</v>
       </c>
       <c r="D2326" t="n">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="E2326" t="n">
-        <v>25.42</v>
+        <v>28.4</v>
       </c>
     </row>
     <row r="2327">
       <c r="A2327" s="2" t="n">
-        <v>46159.83590369458</v>
+        <v>46156</v>
       </c>
       <c r="B2327" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="C2327" t="n">
-        <v>0.98</v>
+        <v>5</v>
       </c>
       <c r="D2327" t="n">
+        <v>72</v>
+      </c>
+      <c r="E2327" t="n">
+        <v>28.1</v>
+      </c>
+    </row>
+    <row r="2328">
+      <c r="A2328" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B2328" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C2328" t="n">
+        <v>8</v>
+      </c>
+      <c r="D2328" t="n">
+        <v>67</v>
+      </c>
+      <c r="E2328" t="n">
+        <v>29.2</v>
+      </c>
+    </row>
+    <row r="2329">
+      <c r="A2329" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B2329" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2329" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2329" t="n">
+        <v>72</v>
+      </c>
+      <c r="E2329" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2330">
+      <c r="A2330" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B2330" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2330" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2330" t="n">
+        <v>76</v>
+      </c>
+      <c r="E2330" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="2331">
+      <c r="A2331" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B2331" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2331" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2331" t="n">
+        <v>76</v>
+      </c>
+      <c r="E2331" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="2332">
+      <c r="A2332" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B2332" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2332" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D2332" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="E2332" t="n">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="2333">
+      <c r="A2333" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B2333" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="C2333" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D2333" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="E2333" t="n">
+        <v>26.6</v>
+      </c>
+    </row>
+    <row r="2334">
+      <c r="A2334" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B2334" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C2334" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D2334" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="E2334" t="n">
+        <v>28.1</v>
+      </c>
+    </row>
+    <row r="2335">
+      <c r="A2335" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B2335" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2335" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="D2335" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="E2335" t="n">
+        <v>29.4</v>
+      </c>
+    </row>
+    <row r="2336">
+      <c r="A2336" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B2336" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2336" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D2336" t="n">
+        <v>79</v>
+      </c>
+      <c r="E2336" t="n">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="2337">
+      <c r="A2337" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B2337" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2337" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D2337" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="E2337" t="n">
+        <v>28.3</v>
+      </c>
+    </row>
+    <row r="2338">
+      <c r="A2338" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="B2338" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2338" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D2338" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="E2338" t="n">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="2339">
+      <c r="A2339" s="2" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B2339" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C2339" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D2339" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="E2339" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2340">
+      <c r="A2340" s="2" t="n">
+        <v>46169</v>
+      </c>
+      <c r="B2340" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2340" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D2340" t="n">
+        <v>69</v>
+      </c>
+      <c r="E2340" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2341">
+      <c r="A2341" s="2" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B2341" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2341" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D2341" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="E2341" t="n">
+        <v>28.1</v>
+      </c>
+    </row>
+    <row r="2342">
+      <c r="A2342" s="2" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B2342" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2342" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D2342" t="n">
+        <v>63</v>
+      </c>
+      <c r="E2342" t="n">
+        <v>29.2</v>
+      </c>
+    </row>
+    <row r="2343">
+      <c r="A2343" s="2" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B2343" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2343" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D2343" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="E2343" t="n">
+        <v>27.6</v>
+      </c>
+    </row>
+    <row r="2344">
+      <c r="A2344" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B2344" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2344" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D2344" t="n">
+        <v>75</v>
+      </c>
+      <c r="E2344" t="n">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="2345">
+      <c r="A2345" s="2" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B2345" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2345" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D2345" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="E2345" t="n">
+        <v>30.3</v>
+      </c>
+    </row>
+    <row r="2346">
+      <c r="A2346" s="2" t="n">
+        <v>46175</v>
+      </c>
+      <c r="B2346" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2346" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D2346" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="E2346" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="2347">
+      <c r="A2347" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B2347" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="C2347" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D2347" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E2347" t="n">
+        <v>27.1</v>
+      </c>
+    </row>
+    <row r="2348">
+      <c r="A2348" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B2348" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="C2348" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D2348" t="n">
+        <v>76</v>
+      </c>
+      <c r="E2348" t="n">
+        <v>28.4</v>
+      </c>
+    </row>
+    <row r="2349">
+      <c r="A2349" s="2" t="n">
+        <v>46178</v>
+      </c>
+      <c r="B2349" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2349" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="D2349" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="E2349" t="n">
+        <v>27.7</v>
+      </c>
+    </row>
+    <row r="2350">
+      <c r="A2350" s="2" t="n">
+        <v>46179</v>
+      </c>
+      <c r="B2350" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C2350" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D2350" t="n">
+        <v>71</v>
+      </c>
+      <c r="E2350" t="n">
+        <v>29.4</v>
+      </c>
+    </row>
+    <row r="2351">
+      <c r="A2351" s="2" t="n">
+        <v>46180</v>
+      </c>
+      <c r="B2351" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C2351" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D2351" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="E2351" t="n">
+        <v>27.6</v>
+      </c>
+    </row>
+    <row r="2352">
+      <c r="A2352" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B2352" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2352" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D2352" t="n">
+        <v>76</v>
+      </c>
+      <c r="E2352" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="2353">
+      <c r="A2353" s="2" t="n">
+        <v>46182</v>
+      </c>
+      <c r="B2353" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2353" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="D2353" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="E2353" t="n">
+        <v>28.1</v>
+      </c>
+    </row>
+    <row r="2354">
+      <c r="A2354" s="2" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B2354" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2354" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="D2354" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="E2354" t="n">
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="2355">
+      <c r="A2355" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B2355" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2355" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D2355" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="E2355" t="n">
+        <v>28.2</v>
+      </c>
+    </row>
+    <row r="2356">
+      <c r="A2356" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B2356" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2356" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D2356" t="n">
+        <v>80</v>
+      </c>
+      <c r="E2356" t="n">
+        <v>27.6</v>
+      </c>
+    </row>
+    <row r="2357">
+      <c r="A2357" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B2357" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2357" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="D2357" t="n">
+        <v>79</v>
+      </c>
+      <c r="E2357" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2358">
+      <c r="A2358" s="2" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B2358" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2358" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D2358" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="E2358" t="n">
+        <v>27.6</v>
+      </c>
+    </row>
+    <row r="2359">
+      <c r="A2359" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B2359" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="C2359" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="D2359" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="E2359" t="n">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="2360">
+      <c r="A2360" s="2" t="n">
+        <v>46189</v>
+      </c>
+      <c r="B2360" t="n">
+        <v>26</v>
+      </c>
+      <c r="C2360" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D2360" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="E2360" t="n">
+        <v>27.4</v>
+      </c>
+    </row>
+    <row r="2361">
+      <c r="A2361" s="2" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B2361" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="C2361" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D2361" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="E2361" t="n">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="2362">
+      <c r="A2362" s="2" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B2362" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="C2362" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D2362" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="E2362" t="n">
+        <v>26.8</v>
+      </c>
+    </row>
+    <row r="2363">
+      <c r="A2363" s="2" t="n">
+        <v>46192</v>
+      </c>
+      <c r="B2363" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C2363" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="D2363" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="E2363" t="n">
+        <v>27.1</v>
+      </c>
+    </row>
+    <row r="2364">
+      <c r="A2364" s="2" t="n">
+        <v>46193</v>
+      </c>
+      <c r="B2364" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="C2364" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D2364" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="E2364" t="n">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="2365">
+      <c r="A2365" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B2365" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="C2365" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="D2365" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="E2365" t="n">
+        <v>27.4</v>
+      </c>
+    </row>
+    <row r="2366">
+      <c r="A2366" s="2" t="n">
+        <v>46195</v>
+      </c>
+      <c r="B2366" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2366" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="D2366" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="E2366" t="n">
+        <v>27.9</v>
+      </c>
+    </row>
+    <row r="2367">
+      <c r="A2367" s="2" t="n">
+        <v>46196</v>
+      </c>
+      <c r="B2367" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2367" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="D2367" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="E2367" t="n">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="2368">
+      <c r="A2368" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B2368" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2368" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D2368" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="E2368" t="n">
+        <v>27.6</v>
+      </c>
+    </row>
+    <row r="2369">
+      <c r="A2369" s="2" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B2369" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2369" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="D2369" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="E2369" t="n">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="2370">
+      <c r="A2370" s="2" t="n">
+        <v>46199</v>
+      </c>
+      <c r="B2370" t="n">
+        <v>22</v>
+      </c>
+      <c r="C2370" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D2370" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="E2370" t="n">
+        <v>26.8</v>
+      </c>
+    </row>
+    <row r="2371">
+      <c r="A2371" s="2" t="n">
+        <v>46200</v>
+      </c>
+      <c r="B2371" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="C2371" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D2371" t="n">
         <v>85</v>
       </c>
-      <c r="E2327" t="n">
-        <v>25.39</v>
+      <c r="E2371" t="n">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="2372">
+      <c r="A2372" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B2372" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2372" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2372" t="n">
+        <v>86</v>
+      </c>
+      <c r="E2372" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2373">
+      <c r="A2373" s="2" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B2373" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2373" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="D2373" t="n">
+        <v>82</v>
+      </c>
+      <c r="E2373" t="n">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="2374">
+      <c r="A2374" s="2" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B2374" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2374" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2374" t="n">
+        <v>80</v>
+      </c>
+      <c r="E2374" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2375">
+      <c r="A2375" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B2375" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2375" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D2375" t="n">
+        <v>78</v>
+      </c>
+      <c r="E2375" t="n">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="2376">
+      <c r="A2376" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B2376" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="C2376" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D2376" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="E2376" t="n">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="2377">
+      <c r="A2377" s="2" t="n">
+        <v>46206</v>
+      </c>
+      <c r="B2377" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2377" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D2377" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="E2377" t="n">
+        <v>28.2</v>
+      </c>
+    </row>
+    <row r="2378">
+      <c r="A2378" s="2" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B2378" t="n">
+        <v>16</v>
+      </c>
+      <c r="C2378" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D2378" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="E2378" t="n">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="2379">
+      <c r="A2379" s="2" t="n">
+        <v>46208</v>
+      </c>
+      <c r="B2379" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="C2379" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D2379" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="E2379" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2380">
+      <c r="A2380" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B2380" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2380" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2380" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="E2380" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="2381">
+      <c r="A2381" s="2" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B2381" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2381" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D2381" t="n">
+        <v>70</v>
+      </c>
+      <c r="E2381" t="n">
+        <v>28.9</v>
+      </c>
+    </row>
+    <row r="2382">
+      <c r="A2382" s="2" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B2382" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2382" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D2382" t="n">
+        <v>66</v>
+      </c>
+      <c r="E2382" t="n">
+        <v>28.9</v>
       </c>
     </row>
   </sheetData>
